--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_12_R2.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_12_R2.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8283</v>
+        <v>6.711</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0726</v>
+        <v>6.1906</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7557</v>
+        <v>0.5204</v>
       </c>
       <c r="G2" t="n">
         <v>3.6093</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2913</v>
+        <v>0.174</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7231</v>
+        <v>-0.6051</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0144</v>
+        <v>0.7791</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9753</v>
+        <v>3.6564</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3653</v>
+        <v>2.4832</v>
       </c>
       <c r="F3" t="n">
-        <v>1.61</v>
+        <v>1.1731</v>
       </c>
       <c r="G3" t="n">
         <v>-0.5600000000000001</v>
@@ -688,13 +688,13 @@
         <v>2.5515</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6049</v>
+        <v>0.286</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0218</v>
+        <v>-0.9039</v>
       </c>
       <c r="U3" t="n">
-        <v>1.6267</v>
+        <v>1.1899</v>
       </c>
       <c r="V3" t="n">
         <v>2.5387</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3081</v>
+        <v>2.745</v>
       </c>
       <c r="E4" t="n">
         <v>2.2989</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0092</v>
+        <v>0.4461</v>
       </c>
       <c r="G4" t="n">
         <v>2.5419</v>
@@ -766,13 +766,13 @@
         <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0688</v>
+        <v>-0.6319</v>
       </c>
       <c r="T4" t="n">
         <v>-1.0376</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0312</v>
+        <v>0.4057</v>
       </c>
       <c r="V4" t="n">
         <v>-0.7886</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>J. PARKER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2879</v>
+        <v>1.2934</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0636</v>
+        <v>0.0684</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2243</v>
+        <v>1.225</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.6755</v>
+        <v>0.131</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.6818</v>
+        <v>-0.6519</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9937</v>
+        <v>0.783</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.01</v>
+        <v>0.7455000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4383</v>
+        <v>-0.9341</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4282</v>
+        <v>1.6796</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6655</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2435</v>
+        <v>0.2822</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.422</v>
+        <v>-0.8966</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0876</v>
+        <v>0.232</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0876</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0873</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0736</v>
+        <v>-0.5895</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0136</v>
+        <v>0.5895</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7886</v>
+        <v>0.9304</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7886</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PARKER</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.159</v>
+        <v>0.7483</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0684</v>
+        <v>-0.6441</v>
       </c>
       <c r="F6" t="n">
-        <v>1.0906</v>
+        <v>1.3924</v>
       </c>
       <c r="G6" t="n">
-        <v>0.131</v>
+        <v>-2.6755</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6519</v>
+        <v>-1.6818</v>
       </c>
       <c r="I6" t="n">
-        <v>0.783</v>
+        <v>-0.9937</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7455000000000001</v>
+        <v>-1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9341</v>
+        <v>-1.4383</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6796</v>
+        <v>0.4282</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-1.6655</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2822</v>
+        <v>-0.2435</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8966</v>
+        <v>-1.422</v>
       </c>
       <c r="P6" t="n">
-        <v>0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1344</v>
+        <v>0.5476</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5895</v>
+        <v>0.3659</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4551</v>
+        <v>0.1817</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9304</v>
+        <v>0.7886</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1418</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. MARINKOVIC</t>
+          <t>A. POKUSEVSKI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0817</v>
+        <v>-1.2795</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7339</v>
+        <v>-2.0199</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6523</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4523</v>
+        <v>-0.1451</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4585</v>
+        <v>0.1861</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9937</v>
+        <v>-0.3312</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4723</v>
+        <v>0.0872</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9005</v>
+        <v>0.0504</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4282</v>
+        <v>0.0368</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.98</v>
+        <v>-0.2323</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5581</v>
+        <v>0.1357</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.422</v>
+        <v>-0.368</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9278</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4428</v>
+        <v>0.1672</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1019</v>
+        <v>0.2124</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5447</v>
+        <v>-0.0452</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. POKUSEVSKI</t>
+          <t>V. MARINKOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7006</v>
+        <v>-1.3848</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.3737</v>
+        <v>-1.9699</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6732</v>
+        <v>0.5851</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1451</v>
+        <v>-2.4523</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1861</v>
+        <v>-1.4585</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3312</v>
+        <v>-0.9937</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0872</v>
+        <v>-0.4723</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0504</v>
+        <v>-0.9005</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0368</v>
+        <v>0.4282</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2323</v>
+        <v>-1.98</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1357</v>
+        <v>-0.5581</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.368</v>
+        <v>-1.422</v>
       </c>
       <c r="P9" t="n">
+        <v>0.9278</v>
+      </c>
+      <c r="Q9" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q9" t="n">
-        <v>-2.3195</v>
-      </c>
       <c r="R9" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2539</v>
+        <v>0.1397</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1415</v>
+        <v>-0.3378</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1125</v>
+        <v>0.4775</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2071</v>
+        <v>-1.6681</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0291</v>
+        <v>-1.5573</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.178</v>
+        <v>-0.1108</v>
       </c>
       <c r="G10" t="n">
         <v>-3.3502</v>
@@ -1234,13 +1234,13 @@
         <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0141</v>
+        <v>0.525</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.275</v>
+        <v>0.1968</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2609</v>
+        <v>0.3282</v>
       </c>
       <c r="V10" t="n">
         <v>-0.9304</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8157</v>
+        <v>-2.9</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0094</v>
+        <v>-3.1274</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1938</v>
+        <v>0.2274</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0036</v>
@@ -1312,13 +1312,13 @@
         <v>2.0876</v>
       </c>
       <c r="S11" t="n">
-        <v>0.51</v>
+        <v>0.4257</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1379</v>
+        <v>0.02</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3721</v>
+        <v>0.4057</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9304</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.8025</v>
+        <v>-3.9705</v>
       </c>
       <c r="E12" t="n">
         <v>-1.4485</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.354</v>
+        <v>-2.522</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2365</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1867</v>
+        <v>0.0187</v>
       </c>
       <c r="T12" t="n">
         <v>-0.7389</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9256</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>-3.2166</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.108299999999998</v>
+        <v>4.108499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2742000000000011</v>
+        <v>0.2740000000000007</v>
       </c>
       <c r="F13" t="n">
         <v>3.834400000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.983700000000001</v>
+        <v>-4.9837</v>
       </c>
       <c r="H13" t="n">
         <v>-3.6622</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.321200000000001</v>
+        <v>-1.3212</v>
       </c>
       <c r="J13" t="n">
         <v>10.2041</v>
@@ -1459,7 +1459,7 @@
         <v>-13.7006</v>
       </c>
       <c r="P13" t="n">
-        <v>8.118400000000001</v>
+        <v>8.118399999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-10.438</v>
@@ -1468,13 +1468,13 @@
         <v>18.5564</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6518</v>
+        <v>1.652</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.4178</v>
+        <v>-3.4177</v>
       </c>
       <c r="U13" t="n">
-        <v>5.0694</v>
+        <v>5.0697</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6779000000000006</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3081</v>
+        <v>5.3075</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3759</v>
+        <v>1.6118</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9322</v>
+        <v>3.6957</v>
       </c>
       <c r="G14" t="n">
         <v>4.9947</v>
@@ -1546,13 +1546,13 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3154</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5816</v>
+        <v>-0.3457</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2662</v>
+        <v>1.0297</v>
       </c>
       <c r="V14" t="n">
         <v>0.7886</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3838</v>
+        <v>2.654</v>
       </c>
       <c r="E15" t="n">
         <v>4.2452</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.8614</v>
+        <v>-1.5913</v>
       </c>
       <c r="G15" t="n">
         <v>2.0909</v>
@@ -1624,13 +1624,13 @@
         <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5474</v>
+        <v>-0.2772</v>
       </c>
       <c r="T15" t="n">
         <v>-0.963</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4156</v>
+        <v>0.6858</v>
       </c>
       <c r="V15" t="n">
         <v>1.0722</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1277</v>
+        <v>1.6661</v>
       </c>
       <c r="E16" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.3204</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0432</v>
+        <v>1.3457</v>
       </c>
       <c r="G16" t="n">
         <v>2.7738</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0224</v>
+        <v>0.516</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.224</v>
+        <v>0.0119</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2016</v>
+        <v>0.5041</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7904</v>
+        <v>0.6852</v>
       </c>
       <c r="E17" t="n">
-        <v>0.361</v>
+        <v>0.479</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4294</v>
+        <v>0.2062</v>
       </c>
       <c r="G17" t="n">
         <v>0.4877</v>
@@ -1780,13 +1780,13 @@
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4314</v>
+        <v>0.3262</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.507</v>
+        <v>-0.389</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9384</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>0.5671</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0265</v>
+        <v>-0.3889</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4351</v>
+        <v>0.9633</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4086</v>
+        <v>-1.3522</v>
       </c>
       <c r="G18" t="n">
         <v>-1.298</v>
@@ -1858,13 +1858,13 @@
         <v>1.1598</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6286</v>
+        <v>0.2133</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1687</v>
+        <v>-0.6405</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7973</v>
+        <v>0.8538</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>V. CANCAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3811</v>
+        <v>-0.4653</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.603</v>
+        <v>-1.091</v>
       </c>
       <c r="F19" t="n">
-        <v>0.222</v>
+        <v>0.6257</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3137</v>
+        <v>-0.0014</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.0733</v>
+        <v>-0.2892</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7596000000000001</v>
+        <v>0.2878</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2903</v>
+        <v>0.2849</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.9978</v>
+        <v>0.1008</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2882</v>
+        <v>0.184</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.604</v>
+        <v>-0.2862</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0755</v>
+        <v>-0.39</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5286</v>
+        <v>0.1038</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7033</v>
+        <v>0.232</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0351</v>
+        <v>-0.2161</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7385</v>
+        <v>0.4481</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4665</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>N. MANNION</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7318</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2513</v>
+        <v>-0.8455</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5195</v>
+        <v>0.3289</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2944</v>
+        <v>0.8462</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3145</v>
+        <v>0.7191</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0201</v>
+        <v>0.1271</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7127</v>
+        <v>2.2366</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.7863</v>
+        <v>1.1091</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0736</v>
+        <v>1.1275</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4183</v>
+        <v>-1.3904</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4718</v>
+        <v>-0.39</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.0535</v>
+        <v>-1.0004</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.4639</v>
+        <v>-2.7834</v>
       </c>
       <c r="R20" t="n">
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4028</v>
+        <v>-0.0639</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0747</v>
+        <v>-0.2987</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4775</v>
+        <v>0.2348</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>0.7886</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. CANCAR</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7341</v>
+        <v>-0.6247</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.091</v>
+        <v>-1.1334</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3569</v>
+        <v>0.5087</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0014</v>
+        <v>-0.2944</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2892</v>
+        <v>-0.3145</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2878</v>
+        <v>0.0201</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2849</v>
+        <v>-0.7127</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1008</v>
+        <v>-0.7863</v>
       </c>
       <c r="L21" t="n">
-        <v>0.184</v>
+        <v>0.0736</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2862</v>
+        <v>0.4183</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.39</v>
+        <v>0.4718</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1038</v>
+        <v>-0.0535</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1598</v>
+        <v>-0.4639</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0369</v>
+        <v>0.51</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2161</v>
+        <v>0.0433</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1792</v>
+        <v>0.4668</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>N. MANNION</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9091</v>
+        <v>-0.6391</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8455</v>
+        <v>-1.0748</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0636</v>
+        <v>0.4357</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8462</v>
+        <v>-0.3137</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7191</v>
+        <v>-1.0733</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1271</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>2.2366</v>
+        <v>0.2903</v>
       </c>
       <c r="K22" t="n">
-        <v>1.1091</v>
+        <v>-0.9978</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1275</v>
+        <v>1.2882</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3904</v>
+        <v>-0.604</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.39</v>
+        <v>-0.0755</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0004</v>
+        <v>-0.5286</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7834</v>
+        <v>-0.4639</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4564</v>
+        <v>0.4452</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2987</v>
+        <v>-0.507</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1577</v>
+        <v>0.9522</v>
       </c>
       <c r="V22" t="n">
-        <v>0.7886</v>
+        <v>-1.4665</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X22" t="n">
-        <v>0.7886</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5038</v>
+        <v>-3.7124</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2233</v>
+        <v>-4.1054</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2805</v>
+        <v>0.393</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5536</v>
@@ -2248,13 +2248,13 @@
         <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3987</v>
+        <v>-0.6073</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.963</v>
+        <v>-0.845</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4358</v>
+        <v>0.2377</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.4851</v>
+        <v>-4.9289</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.322</v>
+        <v>-3.204</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1631</v>
+        <v>-1.7249</v>
       </c>
       <c r="G24" t="n">
         <v>-3.7485</v>
@@ -2326,13 +2326,13 @@
         <v>0.9278</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0407</v>
+        <v>-0.4845</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0376</v>
+        <v>-0.9197</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0031</v>
+        <v>0.4351</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.1085</v>
+        <v>-0.9631000000000003</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.8344</v>
+        <v>-3.834400000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.274</v>
+        <v>2.8712</v>
       </c>
       <c r="G25" t="n">
         <v>4.983699999999999</v>
@@ -2404,16 +2404,16 @@
         <v>10.4381</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6518</v>
+        <v>1.4938</v>
       </c>
       <c r="T25" t="n">
-        <v>-5.069500000000001</v>
+        <v>-5.0695</v>
       </c>
       <c r="U25" t="n">
-        <v>3.4177</v>
+        <v>6.563300000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>0.6778000000000002</v>
+        <v>0.6778000000000004</v>
       </c>
       <c r="W25" t="n">
         <v>4.603400000000001</v>
